--- a/data/trans_dic/P1416-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1416-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 6,66</t>
+          <t>3,97; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,15</t>
+          <t>2,51; 5,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,72</t>
+          <t>1,35; 3,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,18</t>
+          <t>3,94; 7,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,95</t>
+          <t>6,17; 9,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,4</t>
+          <t>3,94; 6,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,62</t>
+          <t>3,63; 6,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,34; 11,57</t>
+          <t>8,8; 11,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,55</t>
+          <t>5,52; 7,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,31</t>
+          <t>3,6; 5,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,82</t>
+          <t>2,95; 4,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 9,57</t>
+          <t>7,26; 9,69</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,2</t>
+          <t>5,78; 8,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,64</t>
+          <t>4,46; 6,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,99</t>
+          <t>3,97; 6,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 12,73</t>
+          <t>9,54; 12,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,1; 12,27</t>
+          <t>9,23; 12,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 9,92</t>
+          <t>7,18; 9,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,86</t>
+          <t>7,4; 9,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,66</t>
+          <t>10,63; 13,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,81; 9,69</t>
+          <t>7,82; 9,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 7,72</t>
+          <t>6,11; 7,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,65</t>
+          <t>5,99; 7,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,71</t>
+          <t>10,43; 12,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,08</t>
+          <t>6,71; 11,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,7</t>
+          <t>4,6; 9,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,28</t>
+          <t>6,19; 11,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,52</t>
+          <t>6,35; 10,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,28</t>
+          <t>8,97; 15,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 13,06</t>
+          <t>7,37; 13,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 13,99</t>
+          <t>8,34; 13,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 16,67</t>
+          <t>12,45; 17,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 12,21</t>
+          <t>8,38; 12,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,28</t>
+          <t>6,42; 10,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 11,88</t>
+          <t>7,89; 11,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,92</t>
+          <t>10,05; 13,21</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,63</t>
+          <t>5,76; 7,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,02</t>
+          <t>4,41; 5,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,76</t>
+          <t>4,25; 5,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 10,84</t>
+          <t>8,57; 10,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 10,59</t>
+          <t>8,64; 10,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,24</t>
+          <t>6,6; 8,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 8,93</t>
+          <t>7,14; 8,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,94</t>
+          <t>11,05; 12,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,88</t>
+          <t>7,51; 8,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 6,85</t>
+          <t>5,74; 6,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,15</t>
+          <t>5,98; 7,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,18</t>
+          <t>10,19; 11,72</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>84453</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>104385</t>
+          <t>116702</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40715; 68696</t>
+          <t>40980; 68754</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25006; 50194</t>
+          <t>24496; 51374</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10608; 28050</t>
+          <t>10177; 26382</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21746; 42016</t>
+          <t>22774; 44083</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81261; 117720</t>
+          <t>81185; 118735</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51691; 85619</t>
+          <t>52743; 84264</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37130; 65864</t>
+          <t>36100; 65455</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>62683; 86987</t>
+          <t>72184; 98126</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131059; 177151</t>
+          <t>129476; 174203</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83544; 122682</t>
+          <t>83293; 123996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52731; 84270</t>
+          <t>51587; 85086</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89222; 121108</t>
+          <t>101483; 135467</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239427</t>
+          <t>247972</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>224443</t>
+          <t>252686</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>463871</t>
+          <t>500658</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97937; 138932</t>
+          <t>97869; 138230</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88282; 130302</t>
+          <t>87516; 130038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85217; 124326</t>
+          <t>82366; 124873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170674; 291016</t>
+          <t>212428; 285460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>144512; 194758</t>
+          <t>146500; 192594</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>125817; 174217</t>
+          <t>126172; 173028</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>148231; 196015</t>
+          <t>147038; 197464</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>155873; 259344</t>
+          <t>229421; 281607</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>256397; 318027</t>
+          <t>256662; 323710</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>224826; 287190</t>
+          <t>227220; 289352</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>244862; 311098</t>
+          <t>243429; 306120</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>359656; 528130</t>
+          <t>456990; 549273</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>59711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>107320</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>146364</t>
+          <t>167031</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36626; 66629</t>
+          <t>37008; 63752</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21722; 46659</t>
+          <t>22111; 45293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35437; 61677</t>
+          <t>33872; 61615</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38802; 68019</t>
+          <t>45197; 77699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42095; 72815</t>
+          <t>42741; 73161</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32296; 59912</t>
+          <t>33815; 60839</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46847; 76832</t>
+          <t>45819; 76435</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79333; 109866</t>
+          <t>91291; 127452</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84409; 125543</t>
+          <t>86118; 125248</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60849; 96630</t>
+          <t>60379; 96049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87681; 130193</t>
+          <t>86456; 130273</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>124146; 168680</t>
+          <t>145289; 190881</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322264</t>
+          <t>339933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>392357</t>
+          <t>444458</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>714620</t>
+          <t>784392</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>193186; 249909</t>
+          <t>188622; 250643</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>150138; 205884</t>
+          <t>150797; 204577</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>142741; 194534</t>
+          <t>143602; 194722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>250475; 373492</t>
+          <t>301150; 380633</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>290318; 357888</t>
+          <t>291854; 358099</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>231609; 292701</t>
+          <t>234372; 295728</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>248597; 315315</t>
+          <t>252284; 316472</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>322608; 434153</t>
+          <t>410013; 479530</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>501629; 590728</t>
+          <t>499853; 593898</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>395235; 477837</t>
+          <t>400343; 480357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>406607; 494260</t>
+          <t>413280; 493470</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>614290; 791593</t>
+          <t>736034; 846863</t>
         </is>
       </c>
     </row>
